--- a/data/raw/inventory/Week 25/Audio_Array/Vendor SOH (SP-API).xlsx
+++ b/data/raw/inventory/Week 25/Audio_Array/Vendor SOH (SP-API).xlsx
@@ -506,12 +506,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FBA79906</t>
+          <t>FBA79448</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>B0FTVVLNS9</t>
+          <t>B0DFMKY4TT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -521,25 +521,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PB-12 (AM-C11+AA-05+AI-04+AH-60-RD)</t>
+          <t>AM-W35</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PB-12</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>6152.0362</v>
+        <v>1984.74951924</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -551,16 +551,16 @@
         <v>25</v>
       </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>4</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>35237.26</v>
+        <v>29115.32</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -571,12 +571,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FBA79965</t>
+          <t>FBA80085</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B0G53PRM34</t>
+          <t>B0GXPBHDRF</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AM-Mix6</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -596,15 +596,15 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>6 channels mixer</t>
+          <t>06 channels Mixer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>4696.526757959999</v>
+        <v>3998.590893</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         <v>25</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -625,7 +625,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>53134.2</v>
+        <v>52433.54</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FBA79379</t>
+          <t>FBA79906</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B0D3LZWTHV</t>
+          <t>B0FTVVLNS9</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -651,25 +651,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AM-C45</t>
+          <t>PB-12 (AM-C11+AA-05+AI-04+AH-60-RD)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dynamic Microphone</t>
+          <t>PB-12</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>2021.262651</v>
+        <v>6152.0362</v>
       </c>
       <c r="I4" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -681,16 +681,16 @@
         <v>25</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>95048.94</v>
+        <v>35237.26</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -701,12 +701,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FBA75675</t>
+          <t>FBA79109</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B0B4G8ZB64</t>
+          <t>B0CM9HYVDM</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -716,25 +716,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AM-C3</t>
+          <t>AM-W18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Speaker Karaoke</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>Microphone with Speaker</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>659.7098370441175</v>
+        <v>612.8989974</v>
       </c>
       <c r="I5" t="n">
-        <v>88</v>
+        <v>186</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -746,16 +746,16 @@
         <v>25</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="O5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P5" t="n">
-        <v>58732.58</v>
+        <v>162340.59</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -766,12 +766,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FBA79983</t>
+          <t>FBA79722</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B0GN321RXQ</t>
+          <t>B0F2HYY7JF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -781,25 +781,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AM-W48 / AM-S6</t>
+          <t>AM-W21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Party Speaker</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dual 12" 160W Bluetooth Party Speaker</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>13607.288</v>
+        <v>2803.686903</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -819,7 +819,9 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>14763.09</v>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>2026-06-20</t>
@@ -829,12 +831,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FBA75689</t>
+          <t>FBA79103</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B0B4G59Y8W</t>
+          <t>B0CM6NTWBP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -844,25 +846,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AM-W13</t>
+          <t>AI-10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>1305.459898830882</v>
+        <v>1499.646483</v>
       </c>
       <c r="I7" t="n">
-        <v>11</v>
+        <v>167</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,16 +876,16 @@
         <v>25</v>
       </c>
       <c r="M7" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>147</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="P7" t="n">
-        <v>18144.32</v>
+        <v>348909.37</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -894,12 +896,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FBA76728</t>
+          <t>FBA75673</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B0BLNCP74M</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -909,7 +911,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AM-C25</t>
+          <t>AM-C1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -924,10 +926,10 @@
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>2157.615343358823</v>
+        <v>1475.964687829412</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1204</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -939,15 +941,17 @@
         <v>25</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>892</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="inlineStr"/>
+        <v>149</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2271771.86</v>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>2026-06-20</t>
@@ -957,12 +961,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FBA79821</t>
+          <t>FBA79816</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B0FJ2JJZL3</t>
+          <t>B0FPR962YS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -972,25 +976,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>UB-01 (AI-04, AM-S1, AA-21, AM-C2)</t>
+          <t>AM-W22</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UB-01</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>9527.5088</v>
+        <v>1679.60406096</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>176</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1002,16 +1006,16 @@
         <v>25</v>
       </c>
       <c r="M9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>167</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>58031.42</v>
+        <v>442894.99</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1022,12 +1026,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FBA79011</t>
+          <t>FBA75680</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0B4G1PXWV</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1037,7 +1041,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AM-C43</t>
+          <t>AM-C6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1047,15 +1051,15 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>XLR Microphone Kit - Boomarm</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>1304.04042</v>
+        <v>1815.59502123</v>
       </c>
       <c r="I10" t="n">
-        <v>143</v>
+        <v>13</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1067,16 +1071,16 @@
         <v>25</v>
       </c>
       <c r="M10" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="P10" t="n">
-        <v>259410.23</v>
+        <v>18794.34</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1087,12 +1091,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FBA79708</t>
+          <t>FBA79831</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B0FFB6YJM1</t>
+          <t>B0FJ8W5Y9Q</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1102,25 +1106,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SB-01</t>
+          <t>GB-04 (AM-C45 + AI-06)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sound Bar</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sound Bar</t>
+          <t>GB-04</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>708</v>
+        <v>4630.8156</v>
       </c>
       <c r="I11" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1132,16 +1136,16 @@
         <v>25</v>
       </c>
       <c r="M11" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>15346.97</v>
+        <v>47190.19</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1152,12 +1156,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FBA78203</t>
+          <t>FBA76862</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B0C4YTNJG7</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1167,25 +1171,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AM-C30</t>
+          <t>AM-C28</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Conference</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>RGB USB Microphone Kit - Tripod</t>
+          <t>Conference Microphone</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>3196.1775</v>
+        <v>874.2436631991176</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>139</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1197,16 +1201,16 @@
         <v>25</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O12" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="P12" t="n">
-        <v>1683.77</v>
+        <v>148733</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1217,12 +1221,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FBA79968</t>
+          <t>FBA79822</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B0G53M9258</t>
+          <t>B0FJ2J6MTF</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1232,25 +1236,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AI-14</t>
+          <t>KB-01 (AM-W32 + AI-12)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>8 channels Mixer</t>
+          <t>KB-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>3065.101673616</v>
+        <v>2630.5268</v>
       </c>
       <c r="I13" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1262,16 +1266,16 @@
         <v>25</v>
       </c>
       <c r="M13" t="n">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>58725.08</v>
+        <v>3775.02</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1282,12 +1286,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FBA79960</t>
+          <t>FBA80007</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
+          <t>B0GN2LHJY4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1297,25 +1301,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AM-W47 Wireless</t>
+          <t>MT-12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Voice Amplifier</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wireless Voice Amplifier</t>
+          <t>12 channels Mixer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>920.65253652</v>
+        <v>4119.760313999999</v>
       </c>
       <c r="I14" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1330,13 +1334,13 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>66674.12</v>
+        <v>79701.3</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1347,12 +1351,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FBA79105</t>
+          <t>FBA76727</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0BLKCDRNB</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1362,25 +1366,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AI-12</t>
+          <t>AM-C24</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>678.1010183999999</v>
+        <v>1676.644024574118</v>
       </c>
       <c r="I15" t="n">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1392,16 +1396,16 @@
         <v>25</v>
       </c>
       <c r="M15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>74095.75999999999</v>
+        <v>2148.73</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -1412,12 +1416,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FBA80085</t>
+          <t>FBA75688</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>B0GXPBHDRF</t>
+          <t>B0B4G763WS</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1427,25 +1431,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>AM-W12</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06 channels Mixer</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>3998.590893</v>
+        <v>1956.963080117647</v>
       </c>
       <c r="I16" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1457,16 +1461,16 @@
         <v>25</v>
       </c>
       <c r="M16" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>52433.54</v>
+        <v>38167.64</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -1477,12 +1481,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FBA78974</t>
+          <t>FBA79964</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B0CF5RRTDJ</t>
+          <t>B0G53KWRWH</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1492,25 +1496,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AA-20</t>
+          <t>AM-Pro12</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>12 channels Mixer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>1107.780080664706</v>
+        <v>13162.63420323</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1525,13 +1529,13 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>24455.75</v>
+        <v>69917.96000000001</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -1542,12 +1546,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FBA79959</t>
+          <t>FBA79447</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>B0G39ZHDYP</t>
+          <t>B0DFMLXD9S</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1557,25 +1561,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>AM-W47 Wired</t>
+          <t>AM-W34</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Voice Amplifier</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wired Voice Amplifier</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>503.35960212</v>
+        <v>2360.3131602</v>
       </c>
       <c r="I18" t="n">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1587,16 +1591,16 @@
         <v>25</v>
       </c>
       <c r="M18" t="n">
-        <v>107</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>78653.23</v>
+        <v>42990.85</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1607,12 +1611,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FBA80005</t>
+          <t>FBA76730</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>B0GW96CQMG</t>
+          <t>B0BLKB6FRR</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1622,25 +1626,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>T-835</t>
+          <t>AM-C27</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Quad UHF Wireless Microphone With Receiver Box</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>6259.394015999999</v>
+        <v>827.5708984229998</v>
       </c>
       <c r="I19" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1652,16 +1656,16 @@
         <v>25</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>118505.16</v>
+        <v>2014.34</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1672,12 +1676,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FBA78424</t>
+          <t>FBA76723</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>B0C55MY66L</t>
+          <t>B0BLKF46QG</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1687,25 +1691,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AM-C37</t>
+          <t>AM-C20</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>USB/XLR Dynamic Mic</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>3103.426797881559</v>
+        <v>1235.473403164659</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1720,13 +1724,13 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>4669.47</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -1737,12 +1741,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FBA79783</t>
+          <t>FBA79959</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0G39ZHDYP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1752,25 +1756,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>AM-C47</t>
+          <t>AM-W47 Wired</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Voice Amplifier</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Boomarm</t>
+          <t>Wired Voice Amplifier</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>1693.3496544</v>
+        <v>503.35960212</v>
       </c>
       <c r="I21" t="n">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1782,16 +1786,16 @@
         <v>25</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="N21" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="O21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>91337.16</v>
+        <v>78653.23</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -1802,12 +1806,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FBK79009</t>
+          <t>FBA79005</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>B0FLYHJ6DK</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1817,25 +1821,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>AM-C41</t>
+          <t>AM-W45</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Conference</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>Wireless Conference Microphone</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>1043.232336</v>
+        <v>2738.484882</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>130</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1847,16 +1851,16 @@
         <v>25</v>
       </c>
       <c r="M22" t="n">
-        <v>32</v>
+        <v>393</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P22" t="n">
-        <v>1245.82</v>
+        <v>473448.05</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -1867,12 +1871,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FBA80009</t>
+          <t>FBA80084</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>B0GW8R2RYM</t>
+          <t>B0GXP97CZG</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1882,25 +1886,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AM-C51</t>
+          <t>BE-4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>04 channels Mixer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>912.8282939999998</v>
+        <v>1948.404289679999</v>
       </c>
       <c r="I23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1912,16 +1916,16 @@
         <v>25</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" t="n">
-        <v>22424.73</v>
+        <v>62914.77</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -1932,12 +1936,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FBA76721</t>
+          <t>FBA80005</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>B0BLKB55BM</t>
+          <t>B0GW96CQMG</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1947,25 +1951,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>AM-C18</t>
+          <t>T-835</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Microphone dynamic</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mobile Microphone</t>
+          <t>Quad UHF Wireless Microphone With Receiver Box</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>2664.193308210882</v>
+        <v>6259.394015999999</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1977,7 +1981,7 @@
         <v>25</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -1985,7 +1989,9 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="P24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>118505.16</v>
+      </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>2026-06-20</t>
@@ -1995,12 +2001,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FBA79908</t>
+          <t>FBA79653</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>B0FTVV1QJY</t>
+          <t>B0DN6LJZBR</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2010,25 +2016,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>PB-14 (AM-C43+AH-40-SL+AI-12)</t>
+          <t>AM-C45 Pro</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PB-14</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>2280.5034</v>
+        <v>2458.088208</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2040,16 +2046,16 @@
         <v>25</v>
       </c>
       <c r="M25" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>27822.15</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2060,12 +2066,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FBA79969</t>
+          <t>FBA79835</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>B0G3B677Z5</t>
+          <t>B0FJ8TWCQZ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2075,7 +2081,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>UB-03 (AM-S1 + AA-22)</t>
+          <t>PB-06 (AA-05 + AM-C44 + AI-04)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2085,12 +2091,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UB-03</t>
+          <t>PB-06</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>5619.632</v>
+        <v>4841.8232</v>
       </c>
       <c r="I26" t="n">
         <v>16</v>
@@ -2105,16 +2111,16 @@
         <v>25</v>
       </c>
       <c r="M26" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>145423.97</v>
+        <v>118574.49</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2125,12 +2131,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FBA79447</t>
+          <t>FBA79846</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>B0DFMLXD9S</t>
+          <t>B0FN7C25VS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2140,25 +2146,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>AM-W34</t>
+          <t>AM-C11X Pro</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>2360.3131602</v>
+        <v>2263.0394</v>
       </c>
       <c r="I27" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2170,16 +2176,16 @@
         <v>25</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>42990.85</v>
+        <v>36141.32</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -2190,12 +2196,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FBA76730</t>
+          <t>FBA78961</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>B0BLKB6FRR</t>
+          <t>B0CBCB9S14</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2205,22 +2211,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AM-C27</t>
+          <t>AM-C40</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>Condenser Mic with Boom Arm</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>827.5708984229998</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>2</v>
@@ -2241,10 +2247,10 @@
         <v>2</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P28" t="n">
-        <v>2014.34</v>
+        <v>4243.48</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -2255,12 +2261,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FBA79909</t>
+          <t>FBA75674</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>B0FVM17Q4W</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2270,25 +2276,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AM-W20</t>
+          <t>AM-C2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>XLR Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>2164.7070972</v>
+        <v>2119.874127397059</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2300,15 +2306,17 @@
         <v>25</v>
       </c>
       <c r="M29" t="n">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="P29" t="n">
+        <v>55783.47</v>
+      </c>
       <c r="Q29" t="inlineStr">
         <is>
           <t>2026-06-20</t>
@@ -2318,12 +2326,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FBA79838</t>
+          <t>FBA79957</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
+          <t>B0G3Q517Y2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2333,25 +2341,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>AH-40 SL</t>
+          <t>AM-W23</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>DJ Headphone</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>DJ Headphone</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>477.9615959999999</v>
+        <v>1566.15254442</v>
       </c>
       <c r="I30" t="n">
-        <v>244</v>
+        <v>55</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2363,16 +2371,16 @@
         <v>25</v>
       </c>
       <c r="M30" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="O30" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="P30" t="n">
-        <v>225305.53</v>
+        <v>129666.14</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -2383,12 +2391,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FBA79655</t>
+          <t>FBA79844</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>B0DN6PFWNK</t>
+          <t>B0FN7DYB2M</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2398,25 +2406,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>AM-C44 Pro</t>
+          <t>PB-08 (AM-C1 + AI-04)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>PB-08</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>3277.450944</v>
+        <v>3358.8228</v>
       </c>
       <c r="I31" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2428,16 +2436,16 @@
         <v>25</v>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P31" t="n">
-        <v>73753.14</v>
+        <v>5033.59</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -2448,12 +2456,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FBA78975</t>
+          <t>FBA79482</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0DXFPM4N2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2463,25 +2471,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AA-21</t>
+          <t>AM-S1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Monitor Speakers Accessories</t>
+          <t>Monitor Speakers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Monitor Speaker Stand Pair</t>
+          <t>Studio Monitor Speaker</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>1722.835557825</v>
+        <v>4486.010979600001</v>
       </c>
       <c r="I32" t="n">
-        <v>146</v>
+        <v>210</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2493,16 +2501,16 @@
         <v>25</v>
       </c>
       <c r="M32" t="n">
-        <v>161</v>
+        <v>65</v>
       </c>
       <c r="N32" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O32" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="P32" t="n">
-        <v>361614.03</v>
+        <v>1349742.81</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -2513,12 +2521,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FBA78961</t>
+          <t>FBA79960</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>B0CBCB9S14</t>
+          <t>B0G3B152FR</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2528,25 +2536,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>AM-C40</t>
+          <t>AM-W47 Wireless</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Voice Amplifier</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Condenser Mic with Boom Arm</t>
+          <t>Wireless Voice Amplifier</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>920.65253652</v>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2561,13 +2569,13 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="O33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>4243.48</v>
+        <v>66674.12</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -2578,12 +2586,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FBA79822</t>
+          <t>FBA79968</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>B0FJ2J6MTF</t>
+          <t>B0G53M9258</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2593,25 +2601,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>KB-01 (AM-W32 + AI-12)</t>
+          <t>AI-14</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>KB-01</t>
+          <t>8 channels Mixer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>2630.5268</v>
+        <v>3065.101673616</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2623,16 +2631,16 @@
         <v>25</v>
       </c>
       <c r="M34" t="n">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
         <v>1</v>
       </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
       <c r="P34" t="n">
-        <v>3775.02</v>
+        <v>58725.08</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -2643,12 +2651,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FBA79957</t>
+          <t>FBA79826</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>B0G3Q517Y2</t>
+          <t>B0FJ2LQT7K</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2658,25 +2666,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AM-W23</t>
+          <t>PB-02 (AI-04 Red + AM-C11 + AA-05)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>PB-02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>1566.15254442</v>
+        <v>5118.2854</v>
       </c>
       <c r="I35" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2691,13 +2699,13 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="O35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>129666.14</v>
+        <v>120811.9</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -2708,12 +2716,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FBA79835</t>
+          <t>FBA79825</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>B0FJ8TWCQZ</t>
+          <t>B0FJ2DT13L</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2723,7 +2731,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>PB-06 (AA-05 + AM-C44 + AI-04)</t>
+          <t>GB-02 (AM-C43 + AI-11)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2733,15 +2741,15 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PB-06</t>
+          <t>GB-02</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>4841.8232</v>
+        <v>1983.58</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2753,16 +2761,16 @@
         <v>25</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N36" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>118574.49</v>
+        <v>39076.66</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -2773,12 +2781,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FBA75692</t>
+          <t>FBA79708</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>B0B4G1HPL5</t>
+          <t>B0FFB6YJM1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2788,25 +2796,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AM-C11</t>
+          <t>SB-01</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Sound Bar</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>USB/XLR Dynamic Mic</t>
+          <t>Sound Bar</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>2975.579697881559</v>
+        <v>708</v>
       </c>
       <c r="I37" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2818,16 +2826,16 @@
         <v>25</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="N37" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>128349.42</v>
+        <v>15346.97</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -2838,12 +2846,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FBA79008</t>
+          <t>FBA78975</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>B0CH4RT4P8</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2853,25 +2861,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>AI-06</t>
+          <t>AA-21</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Monitor Speakers Accessories</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Monitor Speaker Stand Pair</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>2934.090945</v>
+        <v>1722.835557825</v>
       </c>
       <c r="I38" t="n">
-        <v>18</v>
+        <v>146</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2883,16 +2891,16 @@
         <v>25</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="N38" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P38" t="n">
-        <v>46240.07</v>
+        <v>361614.03</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -2903,12 +2911,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FBA79813</t>
+          <t>FBA79655</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>B0FG88HVQ8</t>
+          <t>B0DN6PFWNK</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2918,25 +2926,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>AH-50</t>
+          <t>AM-C44 Pro</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>DJ Headphone</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>DJ Headphone</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>1201.7320128</v>
+        <v>3277.450944</v>
       </c>
       <c r="I39" t="n">
-        <v>481</v>
+        <v>19</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2948,16 +2956,16 @@
         <v>25</v>
       </c>
       <c r="M39" t="n">
-        <v>317</v>
+        <v>4</v>
       </c>
       <c r="N39" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O39" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="P39" t="n">
-        <v>711190.58</v>
+        <v>73753.14</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -2968,12 +2976,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FBA75687</t>
+          <t>FBA79966</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>B0B4G5ZLTB</t>
+          <t>B0G53KWRVW</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2983,25 +2991,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>AM-W11</t>
+          <t>AM-Mix10</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>10 channels mixer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>2857.758705882353</v>
+        <v>5808.86204274</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3013,16 +3021,16 @@
         <v>25</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P40" t="n">
-        <v>1885.92</v>
+        <v>33559.17</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -3033,12 +3041,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FBA80007</t>
+          <t>FBA75676</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>B0GN2LHJY4</t>
+          <t>B0B4DS678Q</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3048,25 +3056,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>MT-12</t>
+          <t>AM-C4</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>12 channels Mixer</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>4119.760313999999</v>
+        <v>1700.734990628047</v>
       </c>
       <c r="I41" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -3081,13 +3089,13 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O41" t="n">
         <v>2</v>
       </c>
       <c r="P41" t="n">
-        <v>79701.3</v>
+        <v>20352.91</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -3098,12 +3106,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FBK79010</t>
+          <t>FBA79965</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>B0FLYJFC22</t>
+          <t>B0G53PRM34</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3113,25 +3121,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>AM-C42</t>
+          <t>AM-Mix6</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Boomarm</t>
+          <t>6 channels mixer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>1499.646483</v>
+        <v>4696.526757959999</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -3143,16 +3151,16 @@
         <v>25</v>
       </c>
       <c r="M42" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>53134.2</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -3163,12 +3171,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FBA79963</t>
+          <t>FBA79836</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>B0G53CB72D</t>
+          <t>B0FJ8Z1W81</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3178,25 +3186,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>AM-Pro8</t>
+          <t>PB-07 (AA-05 + AM-C45 + AI-04)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>8 channels Mixer</t>
+          <t>PB-07</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>12112.09532316</v>
+        <v>4180.2798</v>
       </c>
       <c r="I43" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -3208,16 +3216,16 @@
         <v>25</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>47194.42</v>
+        <v>49777.93</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -3228,12 +3236,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FBA80002</t>
+          <t>FBA79842</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>B0GW96SHSK</t>
+          <t>B0G4DNF8RZ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3243,25 +3251,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>AM-W33 Pro</t>
+          <t>AM-C48</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Single UHF Wireless Microphone With Receiver</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>1825.656588</v>
+        <v>1956.06063</v>
       </c>
       <c r="I44" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -3273,16 +3281,16 @@
         <v>25</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P44" t="n">
-        <v>32713.83</v>
+        <v>129388.63</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -3293,12 +3301,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FBA78960</t>
+          <t>FBA79983</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>B0CBCB82MT</t>
+          <t>B0GN321RXQ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3308,25 +3316,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>AM-C39</t>
+          <t>AM-W48 / AM-S6</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Party Speaker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>XLR Microphone Kit - Tripod</t>
+          <t>Dual 12" 160W Bluetooth Party Speaker</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>734.122339149</v>
+        <v>13607.288</v>
       </c>
       <c r="I45" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -3341,14 +3349,12 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>8</v>
-      </c>
-      <c r="P45" t="n">
-        <v>57361.55</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
           <t>2026-06-20</t>
@@ -3358,12 +3364,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FBA79104</t>
+          <t>FBA75690</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>B0CM6NVLT9</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3373,25 +3379,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>AI-11</t>
+          <t>AM-C10</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Microphone Conference</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Conference Microphone</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>847.6262729999999</v>
+        <v>2311.522194589411</v>
       </c>
       <c r="I46" t="n">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -3403,16 +3409,16 @@
         <v>25</v>
       </c>
       <c r="M46" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O46" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="P46" t="n">
-        <v>108615.8</v>
+        <v>104506.26</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -3423,12 +3429,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FBA79982</t>
+          <t>FBA80004</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>B0GN8MPYPG</t>
+          <t>B0GW92316G</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3438,25 +3444,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>AK-61 Pro</t>
+          <t>AM-W36 Pro</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Electric Keyboard</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61 Key Electronic Keyboard With LCD DIsplay</t>
+          <t>Dual UHF Wireless Microphone With Receiver Box</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>3317.4116676</v>
+        <v>4694.545512</v>
       </c>
       <c r="I47" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -3468,16 +3474,16 @@
         <v>25</v>
       </c>
       <c r="M47" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>61519.1</v>
+        <v>89138.53999999999</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -3488,12 +3494,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FBA79823</t>
+          <t>FBA79827</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>B0FJ2HZCVN</t>
+          <t>B0FJ8S5XJ8</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3503,7 +3509,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>PB-01 (AM-C11 + AI-04)</t>
+          <t>PB-03 (AI-04 Red + AM-C11 x 2)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3513,15 +3519,15 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>PB-01</t>
+          <t>PB-03</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>4859.948</v>
+        <v>7722.439199999999</v>
       </c>
       <c r="I48" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -3539,10 +3545,10 @@
         <v>12</v>
       </c>
       <c r="O48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>82498.16</v>
+        <v>155003.82</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -3553,12 +3559,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FBA79833</t>
+          <t>FBA75675</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>B0FJ8PZ9H7</t>
+          <t>B0B4G8ZB64</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3568,25 +3574,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>PB-04 (AI-04 Red + AM-C44 x 2)</t>
+          <t>AM-C3</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>PB-04</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>7169.514799999999</v>
+        <v>659.7098370441175</v>
       </c>
       <c r="I49" t="n">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -3598,16 +3604,16 @@
         <v>25</v>
       </c>
       <c r="M49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N49" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O49" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="P49" t="n">
-        <v>81102.49000000001</v>
+        <v>58732.58</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -3618,12 +3624,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FBA79444</t>
+          <t>FBA78976</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>B0DFMLQBMC</t>
+          <t>B0CF5SHL15</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3633,25 +3639,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>AM-W20</t>
+          <t>AA-22</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Monitor Speakers Accessories</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>Monitor Speaker Stand Pair</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>2164.7070972</v>
+        <v>1722.835557825</v>
       </c>
       <c r="I50" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -3663,16 +3669,16 @@
         <v>25</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N50" t="n">
+        <v>6</v>
+      </c>
+      <c r="O50" t="n">
         <v>5</v>
       </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
       <c r="P50" t="n">
-        <v>12578.82</v>
+        <v>49262.39</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -3683,12 +3689,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FBA79964</t>
+          <t>FBA78973</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>B0G53KWRWH</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3698,25 +3704,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AM-Pro12</t>
+          <t>AA-19</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>12 channels Mixer</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>13162.63420323</v>
+        <v>1960.237563966397</v>
       </c>
       <c r="I51" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -3728,16 +3734,16 @@
         <v>25</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P51" t="n">
-        <v>69917.96000000001</v>
+        <v>185097.36</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -3748,12 +3754,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FBA80010</t>
+          <t>FBA79840</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>B0GW8ZQRFK</t>
+          <t>B0FQBWV1ST</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3763,25 +3769,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>AM-C52</t>
+          <t>AH-60-RD</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Headphone</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>Headphone</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>912.8282939999998</v>
+        <v>1092.483648</v>
       </c>
       <c r="I52" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -3793,16 +3799,16 @@
         <v>25</v>
       </c>
       <c r="M52" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N52" t="n">
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P52" t="n">
-        <v>12458.18</v>
+        <v>61960.89</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -3813,12 +3819,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FBA79832</t>
+          <t>FBA75681</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>B0FJ8S53GW</t>
+          <t>B0B4FZS38V</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3828,25 +3834,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>GB-05 (AM-C43 + AI-06)</t>
+          <t>AM-C7</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>GB-05</t>
+          <t>USB Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>3909.104</v>
+        <v>2051.276637829411</v>
       </c>
       <c r="I53" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -3861,13 +3867,13 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>88086.16</v>
+        <v>2050.99</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -3878,12 +3884,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FBA79827</t>
+          <t>FBA79972</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>B0FJ8S5XJ8</t>
+          <t>B0GCP1J2HC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3893,25 +3899,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>PB-03 (AI-04 Red + AM-C11 x 2)</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>PB-03</t>
+          <t>8 channels Mixer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>7722.439199999999</v>
+        <v>4119.760313999999</v>
       </c>
       <c r="I54" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -3923,16 +3929,16 @@
         <v>25</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
         <v>12</v>
       </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
       <c r="P54" t="n">
-        <v>155003.82</v>
+        <v>29712.85</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -3943,12 +3949,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FBA79846</t>
+          <t>FBK79009</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>B0FN7C25VS</t>
+          <t>B0FLYHJ6DK</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3958,25 +3964,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>AM-C11X Pro</t>
+          <t>AM-C41</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>2263.0394</v>
+        <v>1043.232336</v>
       </c>
       <c r="I55" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -3988,16 +3994,16 @@
         <v>25</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="N55" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>36141.32</v>
+        <v>1245.82</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -4073,12 +4079,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FBA78976</t>
+          <t>FBA78925</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>B0CF5SHL15</t>
+          <t>B0CBC7QMNV</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4088,25 +4094,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>AA-22</t>
+          <t>AM-C11X</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Monitor Speakers Accessories</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Monitor Speaker Stand Pair</t>
+          <t>XLR Dynamic Mic</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>1722.835557825</v>
+        <v>2173.4007</v>
       </c>
       <c r="I57" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -4118,16 +4124,16 @@
         <v>25</v>
       </c>
       <c r="M57" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O57" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>49262.39</v>
+        <v>65555</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -4138,12 +4144,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FBA79446</t>
+          <t>FBA79694</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>B0DFMMTWLY</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4153,25 +4159,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>AM-W33</t>
+          <t>AA-26</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>1194.50102472</v>
+        <v>260.808084</v>
       </c>
       <c r="I58" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -4183,16 +4189,16 @@
         <v>25</v>
       </c>
       <c r="M58" t="n">
-        <v>3</v>
+        <v>526</v>
       </c>
       <c r="N58" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="P58" t="n">
-        <v>73745.48</v>
+        <v>41253.26</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -4203,12 +4209,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FBA79356</t>
+          <t>FBA79979</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>B0D3Q2T5XX</t>
+          <t>B0GN8RQJRG</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4218,22 +4224,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>AA-19WL</t>
+          <t>AK-37-B</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Electric Keyboard</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>37 Key Electronic Keyboard Black</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>2973.2121576</v>
+        <v>2261.3068296</v>
       </c>
       <c r="I59" t="n">
         <v>13</v>
@@ -4248,16 +4254,16 @@
         <v>25</v>
       </c>
       <c r="M59" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="N59" t="n">
         <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P59" t="n">
-        <v>41639.04</v>
+        <v>36349.7</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -4268,12 +4274,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FBA79826</t>
+          <t>FBA79446</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>B0FJ2LQT7K</t>
+          <t>B0DFMMTWLY</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4283,25 +4289,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>PB-02 (AI-04 Red + AM-C11 + AA-05)</t>
+          <t>AM-W33</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>PB-02</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>5118.2854</v>
+        <v>1194.50102472</v>
       </c>
       <c r="I60" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -4313,16 +4319,16 @@
         <v>25</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N60" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>120811.9</v>
+        <v>73745.48</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -4333,12 +4339,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FBA79831</t>
+          <t>FBA79379</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>B0FJ8W5Y9Q</t>
+          <t>B0D3LZWTHV</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4348,25 +4354,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>GB-04 (AM-C45 + AI-06)</t>
+          <t>AM-C45</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>GB-04</t>
+          <t>Dynamic Microphone</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>4630.8156</v>
+        <v>2021.262651</v>
       </c>
       <c r="I61" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -4378,16 +4384,16 @@
         <v>25</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N61" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P61" t="n">
-        <v>47190.19</v>
+        <v>95048.94</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -4398,12 +4404,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FBA75683</t>
+          <t>FBA79834</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>B0B4G94VP3</t>
+          <t>B0FJ8T4WXM</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4413,25 +4419,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>AA-03</t>
+          <t>PB-05 (AA-05 + AM-C11 + AI-04)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>PB-05</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>179.9635942941177</v>
+        <v>5118.2854</v>
       </c>
       <c r="I62" t="n">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -4443,16 +4449,16 @@
         <v>25</v>
       </c>
       <c r="M62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N62" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O62" t="n">
         <v>5</v>
       </c>
       <c r="P62" t="n">
-        <v>23981.49</v>
+        <v>36704.9</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -4463,12 +4469,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FBA75680</t>
+          <t>FBA79982</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>B0B4G1PXWV</t>
+          <t>B0GN8MPYPG</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4478,25 +4484,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>AM-C6</t>
+          <t>AK-61 Pro</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Electric Keyboard</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>61 Key Electronic Keyboard With LCD DIsplay</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>1815.59502123</v>
+        <v>3317.4116676</v>
       </c>
       <c r="I63" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -4508,16 +4514,16 @@
         <v>25</v>
       </c>
       <c r="M63" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N63" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P63" t="n">
-        <v>18794.34</v>
+        <v>61519.1</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -4528,12 +4534,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FBA79979</t>
+          <t>FBA79355</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>B0GN8RQJRG</t>
+          <t>B0D3M86SH1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4543,25 +4549,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>AK-37-B</t>
+          <t>AA-19BL</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Electric Keyboard</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>37 Key Electronic Keyboard Black</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>2261.3068296</v>
+        <v>2973.2121576</v>
       </c>
       <c r="I64" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -4573,16 +4579,16 @@
         <v>25</v>
       </c>
       <c r="M64" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O64" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P64" t="n">
-        <v>36349.7</v>
+        <v>57654.05</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -4658,12 +4664,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FBA79841</t>
+          <t>FBA79380</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>B0FQBTRM28</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4673,25 +4679,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>AH-60-BL</t>
+          <t>AM-C46</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Headphone</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Headphone</t>
+          <t>Condenser Mic with Boom Arm</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>1092.483648</v>
+        <v>2021.262651</v>
       </c>
       <c r="I66" t="n">
-        <v>51</v>
+        <v>292</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -4703,16 +4709,16 @@
         <v>25</v>
       </c>
       <c r="M66" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="N66" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="O66" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="P66" t="n">
-        <v>79000.14</v>
+        <v>776119.11</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -4723,12 +4729,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FBA75684</t>
+          <t>FBA79010</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>B0B4G7VWXD</t>
+          <t>B0CH4T2BJD</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4738,25 +4744,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>AA-04</t>
+          <t>AM-C42</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>USB Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>871.9473036705882</v>
+        <v>1499.646483</v>
       </c>
       <c r="I67" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -4768,16 +4774,16 @@
         <v>25</v>
       </c>
       <c r="M67" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N67" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O67" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="P67" t="n">
-        <v>49936.45</v>
+        <v>35258.95</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -4788,12 +4794,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FBA79482</t>
+          <t>FBA78206</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>B0DXFPM4N2</t>
+          <t>B0C4YSV3XL</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4803,25 +4809,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>AM-S1</t>
+          <t>AM-W15</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Monitor Speakers</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Studio Monitor Speaker</t>
+          <t>Wireless Mic with Charging Case</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>4486.010979600001</v>
+        <v>11761.9332</v>
       </c>
       <c r="I68" t="n">
-        <v>210</v>
+        <v>2</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -4833,16 +4839,16 @@
         <v>25</v>
       </c>
       <c r="M68" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="P68" t="n">
-        <v>1349742.81</v>
+        <v>11268.54</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -4853,12 +4859,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FBA79842</t>
+          <t>FBA79783</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>B0G4DNF8RZ</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4868,25 +4874,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>AM-C48</t>
+          <t>AM-C47</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>USB Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>1956.06063</v>
+        <v>1693.3496544</v>
       </c>
       <c r="I69" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -4898,16 +4904,16 @@
         <v>25</v>
       </c>
       <c r="M69" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N69" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O69" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P69" t="n">
-        <v>129388.63</v>
+        <v>91337.16</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -4918,12 +4924,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FBA78925</t>
+          <t>FBA79105</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>B0CBC7QMNV</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4933,25 +4939,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>AM-C11X</t>
+          <t>AI-12</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>XLR Dynamic Mic</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>2173.4007</v>
+        <v>678.1010183999999</v>
       </c>
       <c r="I70" t="n">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -4963,16 +4969,16 @@
         <v>25</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N70" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P70" t="n">
-        <v>65555</v>
+        <v>74095.75999999999</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -4983,12 +4989,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FBA80004</t>
+          <t>FBA79996</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>B0GW92316G</t>
+          <t>B0GW8Z556N</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4998,25 +5004,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>AM-W36 Pro</t>
+          <t>AM-C49</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dual UHF Wireless Microphone With Receiver Box</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>4694.545512</v>
+        <v>534.6565721999999</v>
       </c>
       <c r="I71" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -5028,7 +5034,7 @@
         <v>25</v>
       </c>
       <c r="M71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N71" t="n">
         <v>0</v>
@@ -5037,7 +5043,7 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>89138.53999999999</v>
+        <v>9974.469999999999</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -5048,12 +5054,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FBA76414</t>
+          <t>FBA79838</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0FQBX8J17</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5063,25 +5069,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>AA-05</t>
+          <t>AH-40 SL</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>DJ Headphone</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>DJ Headphone</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>280.0829144294117</v>
+        <v>477.9615959999999</v>
       </c>
       <c r="I72" t="n">
-        <v>202</v>
+        <v>244</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -5093,16 +5099,16 @@
         <v>25</v>
       </c>
       <c r="M72" t="n">
-        <v>135</v>
+        <v>8</v>
       </c>
       <c r="N72" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="P72" t="n">
-        <v>94246.5</v>
+        <v>225305.53</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -5113,12 +5119,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FBA79847</t>
+          <t>FBA79356</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>B0FN7FYZM3</t>
+          <t>B0D3Q2T5XX</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5128,25 +5134,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>PB-09 (AM-C45 + AI-06 + AA-05)</t>
+          <t>AA-19WL</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>PB-09</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>4889.153</v>
+        <v>2973.2121576</v>
       </c>
       <c r="I73" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -5158,16 +5164,16 @@
         <v>25</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N73" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>39150.73</v>
+        <v>41639.04</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -5178,12 +5184,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FBA75688</t>
+          <t>FBA79064</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>B0B4G763WS</t>
+          <t>B0CJR76Y7G</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5193,25 +5199,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>AM-W12</t>
+          <t>AA-25</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>1956.963080117647</v>
+        <v>326.010105</v>
       </c>
       <c r="I74" t="n">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -5226,13 +5232,13 @@
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>38167.64</v>
+        <v>34134.14</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -5243,12 +5249,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FBA79009</t>
+          <t>FBA79961</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>B0CH4PMR8K</t>
+          <t>B0G53H49BS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5258,25 +5264,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>AM-C41</t>
+          <t>AI-13</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>4 channels Mixer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>1043.232336</v>
+        <v>1544.91011775</v>
       </c>
       <c r="I75" t="n">
-        <v>32</v>
+        <v>168</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -5288,16 +5294,16 @@
         <v>25</v>
       </c>
       <c r="M75" t="n">
-        <v>2</v>
+        <v>597</v>
       </c>
       <c r="N75" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O75" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="P75" t="n">
-        <v>39920.09</v>
+        <v>339472.5</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -5308,12 +5314,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FBA79016</t>
+          <t>FBA79008</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>B0CH4R1V6S</t>
+          <t>B0CH4RT4P8</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5323,25 +5329,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>AM-C3a</t>
+          <t>AI-06</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>521.6161679999999</v>
+        <v>2934.090945</v>
       </c>
       <c r="I76" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -5356,13 +5362,13 @@
         <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="O76" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P76" t="n">
-        <v>21130.15</v>
+        <v>46240.07</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -5373,12 +5379,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FBA75673</t>
+          <t>FBA75683</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0B4G94VP3</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5388,25 +5394,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>AM-C1</t>
+          <t>AA-03</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Boomarm</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>1475.964687829412</v>
+        <v>179.9635942941177</v>
       </c>
       <c r="I77" t="n">
-        <v>1204</v>
+        <v>72</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -5418,16 +5424,16 @@
         <v>25</v>
       </c>
       <c r="M77" t="n">
-        <v>892</v>
+        <v>6</v>
       </c>
       <c r="N77" t="n">
-        <v>263</v>
+        <v>2</v>
       </c>
       <c r="O77" t="n">
-        <v>149</v>
+        <v>5</v>
       </c>
       <c r="P77" t="n">
-        <v>2271771.86</v>
+        <v>23981.49</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -5438,12 +5444,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FBA75690</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5453,25 +5459,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>AM-C10</t>
+          <t>AI-04 Red</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Microphone Conference</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Conference Microphone</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>2311.522194589411</v>
+        <v>2165.574481998618</v>
       </c>
       <c r="I78" t="n">
-        <v>36</v>
+        <v>600</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -5483,16 +5489,16 @@
         <v>25</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="N78" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="O78" t="n">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="P78" t="n">
-        <v>104506.26</v>
+        <v>2093901.41</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -5503,12 +5509,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>FBA79967</t>
+          <t>FBA76597</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>B0G2C2RCXN</t>
+          <t>B0BQ7H7418</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5518,25 +5524,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>AM-W19</t>
+          <t>AA-06</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>1159.29193338</v>
+        <v>598.3056269558823</v>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -5548,16 +5554,16 @@
         <v>25</v>
       </c>
       <c r="M79" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="P79" t="n">
-        <v>1481.65</v>
+        <v>22410.33</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -5568,12 +5574,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FBA80084</t>
+          <t>FBA79958</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>B0GXP97CZG</t>
+          <t>B0G3Q59X8C</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5583,25 +5589,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>BE-4</t>
+          <t>AM-W24</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>04 channels Mixer</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>1948.404289679999</v>
+        <v>905.00405148</v>
       </c>
       <c r="I80" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -5613,16 +5619,16 @@
         <v>25</v>
       </c>
       <c r="M80" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P80" t="n">
-        <v>62914.77</v>
+        <v>67344.32000000001</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -5633,12 +5639,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FBA78206</t>
+          <t>FBA78960</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>B0C4YSV3XL</t>
+          <t>B0CBCB82MT</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5648,25 +5654,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>AM-W15</t>
+          <t>AM-C39</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Wireless Mic with Charging Case</t>
+          <t>XLR Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>11761.9332</v>
+        <v>734.122339149</v>
       </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -5681,13 +5687,13 @@
         <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O81" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P81" t="n">
-        <v>11268.54</v>
+        <v>57361.55</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -5698,12 +5704,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FBA78973</t>
+          <t>FBA78974</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0CF5RRTDJ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5713,7 +5719,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>AA-19</t>
+          <t>AA-20</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5728,10 +5734,10 @@
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>1960.237563966397</v>
+        <v>1107.780080664706</v>
       </c>
       <c r="I82" t="n">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -5743,16 +5749,16 @@
         <v>25</v>
       </c>
       <c r="M82" t="n">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P82" t="n">
-        <v>185097.36</v>
+        <v>24455.75</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -5763,12 +5769,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FBA76727</t>
+          <t>FBA79107</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>B0BLKCDRNB</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5778,25 +5784,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>AM-C24</t>
+          <t>AM-W17</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>1676.644024574118</v>
+        <v>1043.232336</v>
       </c>
       <c r="I83" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -5811,13 +5817,13 @@
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="O83" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="P83" t="n">
-        <v>2148.73</v>
+        <v>66470.32000000001</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -5828,12 +5834,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FBA79905</t>
+          <t>FBA76722</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>B0FTVSH458</t>
+          <t>B0BLKDC4PP</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5843,25 +5849,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>PB-11 (AM-C44+AA-05+AH-45-BK)</t>
+          <t>AM-C19</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>PB-11</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>3425.8468</v>
+        <v>1642.572937873306</v>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -5876,14 +5882,12 @@
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="P84" t="n">
-        <v>10486.71</v>
-      </c>
+      <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr">
         <is>
           <t>2026-06-20</t>
@@ -5893,12 +5897,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FBA79995</t>
+          <t>FBA79815</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>B0GW8VBCBL</t>
+          <t>B0FPR7VFCH</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5908,25 +5912,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>AM-C50</t>
+          <t>AM-W19</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>534.6565721999999</v>
+        <v>1159.29193338</v>
       </c>
       <c r="I85" t="n">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -5941,13 +5945,13 @@
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>12468.08</v>
+        <v>75563.99000000001</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -5958,12 +5962,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FBA79816</t>
+          <t>FBA79847</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
+          <t>B0FN7FYZM3</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5973,25 +5977,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>AM-W22</t>
+          <t>PB-09 (AM-C45 + AI-06 + AA-05)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>PB-09</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>1679.60406096</v>
+        <v>4889.153</v>
       </c>
       <c r="I86" t="n">
-        <v>176</v>
+        <v>8</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -6006,13 +6010,13 @@
         <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>167</v>
+        <v>7</v>
       </c>
       <c r="O86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>442894.99</v>
+        <v>39150.73</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -6023,12 +6027,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FBA79824</t>
+          <t>FBA79908</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>B0FJ2K95XT</t>
+          <t>B0FTVV1QJY</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6038,7 +6042,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>GB-01 (AM-C43 +AI-10)</t>
+          <t>PB-14 (AM-C43+AH-40-SL+AI-12)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -6048,15 +6052,15 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>GB-01</t>
+          <t>PB-14</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>2585.9936</v>
+        <v>2280.5034</v>
       </c>
       <c r="I87" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -6068,16 +6072,16 @@
         <v>25</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N87" t="n">
         <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P87" t="n">
-        <v>71307.37</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -6088,12 +6092,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FBA79961</t>
+          <t>FBA78203</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>B0G53H49BS</t>
+          <t>B0C4YTNJG7</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6103,25 +6107,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>AI-13</t>
+          <t>AM-C30</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>4 channels Mixer</t>
+          <t>RGB USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>1544.91011775</v>
+        <v>3196.1775</v>
       </c>
       <c r="I88" t="n">
-        <v>168</v>
+        <v>1</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -6133,16 +6137,16 @@
         <v>25</v>
       </c>
       <c r="M88" t="n">
-        <v>597</v>
+        <v>1</v>
       </c>
       <c r="N88" t="n">
         <v>1</v>
       </c>
       <c r="O88" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="P88" t="n">
-        <v>339472.5</v>
+        <v>1683.77</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -6153,12 +6157,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FBA79904</t>
+          <t>FBA79980</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>B0FTVQQVDC</t>
+          <t>B0GN8MMKY1</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6168,25 +6172,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>PB-10 (AM-C2+AI-04+AH-60-BL)</t>
+          <t>AK-37-W</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Electric Keyboard</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>PB-10</t>
+          <t>37 Key Electronic Keyboard White</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>4986.467599999999</v>
+        <v>2335.8554064</v>
       </c>
       <c r="I89" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -6198,16 +6202,16 @@
         <v>25</v>
       </c>
       <c r="M89" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P89" t="n">
-        <v>276512.04</v>
+        <v>30757.44</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -6218,12 +6222,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>FBA79722</t>
+          <t>FBA79845</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>B0F2HYY7JF</t>
+          <t>B0FN7B3KWS</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6233,25 +6237,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>AM-W21</t>
+          <t>UB-02 (AM-S1 + AA-21)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>UB-02</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>2803.686903</v>
+        <v>5836.846399999999</v>
       </c>
       <c r="I90" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -6263,16 +6267,16 @@
         <v>25</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N90" t="n">
         <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P90" t="n">
-        <v>14763.09</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -6283,12 +6287,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FBA75676</t>
+          <t>FBA79654</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>B0B4DS678Q</t>
+          <t>B0DN6MNS1X</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6298,25 +6302,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>AM-C4</t>
+          <t>AM-C11 Pro</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>1700.734990628047</v>
+        <v>3140.890488</v>
       </c>
       <c r="I91" t="n">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -6331,13 +6335,13 @@
         <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>2</v>
+        <v>79</v>
       </c>
       <c r="O91" t="n">
         <v>2</v>
       </c>
       <c r="P91" t="n">
-        <v>20352.91</v>
+        <v>298226.44</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -6348,12 +6352,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>FBA79815</t>
+          <t>FBA79106</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>B0FPR7VFCH</t>
+          <t>B0CM9KJZWQ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6363,25 +6367,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>AM-W19</t>
+          <t>AM-C44</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>Dynamic Microphone</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>1159.29193338</v>
+        <v>2738.484882</v>
       </c>
       <c r="I92" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -6393,16 +6397,16 @@
         <v>25</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N92" t="n">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P92" t="n">
-        <v>75563.99000000001</v>
+        <v>113110.12</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -6413,12 +6417,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA79848</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0GN97RFPR</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6428,25 +6432,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>AI-04 Red</t>
+          <t>AM-S2</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Monitor Speakers</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Studio Monitor Speaker</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>2165.574481998618</v>
+        <v>3748.5845172</v>
       </c>
       <c r="I93" t="n">
-        <v>600</v>
+        <v>319</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -6458,16 +6462,16 @@
         <v>25</v>
       </c>
       <c r="M93" t="n">
-        <v>280</v>
+        <v>191</v>
       </c>
       <c r="N93" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>86</v>
+        <v>5</v>
       </c>
       <c r="P93" t="n">
-        <v>2093901.41</v>
+        <v>1628020.69</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -6478,12 +6482,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FBA76597</t>
+          <t>FBA79444</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>B0BQ7H7418</t>
+          <t>B0DFMLQBMC</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6493,25 +6497,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>AA-06</t>
+          <t>AM-W20</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>598.3056269558823</v>
+        <v>2164.7070972</v>
       </c>
       <c r="I94" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -6523,16 +6527,16 @@
         <v>25</v>
       </c>
       <c r="M94" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
         <v>5</v>
       </c>
       <c r="O94" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>22410.33</v>
+        <v>12578.82</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -6543,12 +6547,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FBA79109</t>
+          <t>FBA75677</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>B0CM9HYVDM</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6558,25 +6562,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>AM-W18</t>
+          <t>AM-C5</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Speaker Karaoke</t>
+          <t>Microphone Conference</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Microphone with Speaker</t>
+          <t>Conference Microphone</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>612.8989974</v>
+        <v>1291.959696295941</v>
       </c>
       <c r="I95" t="n">
-        <v>186</v>
+        <v>67</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -6588,16 +6592,16 @@
         <v>25</v>
       </c>
       <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="n">
         <v>6</v>
       </c>
-      <c r="N95" t="n">
-        <v>47</v>
-      </c>
       <c r="O95" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P95" t="n">
-        <v>162340.59</v>
+        <v>113875.82</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -6608,12 +6612,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FBA79445</t>
+          <t>FBA79963</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>B0DFMLS8JG</t>
+          <t>B0G53CB72D</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6623,25 +6627,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>AM-W32</t>
+          <t>AM-Pro8</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>8 channels Mixer</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>2167.31517804</v>
+        <v>12112.09532316</v>
       </c>
       <c r="I96" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -6659,10 +6663,10 @@
         <v>1</v>
       </c>
       <c r="O96" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>62976.32</v>
+        <v>47194.42</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -6673,12 +6677,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>FBA80003</t>
+          <t>FBA76721</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>B0GW92TTMS</t>
+          <t>B0BLKB55BM</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6688,25 +6692,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>AM-W32 Pro</t>
+          <t>AM-C18</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Microphone dynamic</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dual UHF Wireless Microphone With Receiver</t>
+          <t>Mobile Microphone</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>3129.697008</v>
+        <v>2664.193308210882</v>
       </c>
       <c r="I97" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -6726,9 +6730,7 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="P97" t="n">
-        <v>61869.39</v>
-      </c>
+      <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr">
         <is>
           <t>2026-06-20</t>
@@ -6738,12 +6740,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FBA79845</t>
+          <t>FBA79108</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>B0FN7B3KWS</t>
+          <t>B0CM9L1QZG</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6753,25 +6755,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>UB-02 (AM-S1 + AA-21)</t>
+          <t>AM-W16</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>UB-02</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>5836.846399999999</v>
+        <v>756.3434436</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -6783,16 +6785,16 @@
         <v>25</v>
       </c>
       <c r="M98" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="O98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>48344.26</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -6868,12 +6870,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>FBA79653</t>
+          <t>FBA79833</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>B0DN6LJZBR</t>
+          <t>B0FJ8PZ9H7</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6883,25 +6885,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>AM-C45 Pro</t>
+          <t>PB-04 (AI-04 Red + AM-C44 x 2)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>PB-04</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>2458.088208</v>
+        <v>7169.514799999999</v>
       </c>
       <c r="I100" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -6913,16 +6915,16 @@
         <v>25</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N100" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O100" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P100" t="n">
-        <v>27822.15</v>
+        <v>81102.49000000001</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -6933,12 +6935,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FBA79010</t>
+          <t>FBA76863</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>B0CH4T2BJD</t>
+          <t>B0BPM2T7BQ</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6948,25 +6950,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>AM-C42</t>
+          <t>AI-03</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Boomarm</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>1499.646483</v>
+        <v>2179.9269789525</v>
       </c>
       <c r="I101" t="n">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -6978,16 +6980,16 @@
         <v>25</v>
       </c>
       <c r="M101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N101" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O101" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P101" t="n">
-        <v>35258.95</v>
+        <v>172634.98</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -6998,12 +7000,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>FBA79834</t>
+          <t>FBA76414</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>B0FJ8T4WXM</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -7013,25 +7015,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>PB-05 (AA-05 + AM-C11 + AI-04)</t>
+          <t>AA-05</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>PB-05</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>5118.2854</v>
+        <v>280.0829144294117</v>
       </c>
       <c r="I102" t="n">
-        <v>5</v>
+        <v>202</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -7043,16 +7045,16 @@
         <v>25</v>
       </c>
       <c r="M102" t="n">
-        <v>5</v>
+        <v>135</v>
       </c>
       <c r="N102" t="n">
         <v>5</v>
       </c>
       <c r="O102" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="P102" t="n">
-        <v>36704.9</v>
+        <v>94246.5</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -7063,12 +7065,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>FBA79380</t>
+          <t>FBA75678</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0B4G8PH2P</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -7078,25 +7080,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>AM-C46</t>
+          <t>AA-01</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Condenser Mic with Boom Arm</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>2021.262651</v>
+        <v>1224.499030661912</v>
       </c>
       <c r="I103" t="n">
-        <v>292</v>
+        <v>25</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -7108,16 +7110,16 @@
         <v>25</v>
       </c>
       <c r="M103" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="N103" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="O103" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="P103" t="n">
-        <v>776119.11</v>
+        <v>36692.4</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -7128,12 +7130,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>FBA79966</t>
+          <t>FBA79011</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>B0G53KWRVW</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -7143,25 +7145,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>AM-Mix10</t>
+          <t>AM-C43</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>10 channels mixer</t>
+          <t>XLR Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>5808.86204274</v>
+        <v>1304.04042</v>
       </c>
       <c r="I104" t="n">
-        <v>4</v>
+        <v>143</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -7173,16 +7175,16 @@
         <v>25</v>
       </c>
       <c r="M104" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O104" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="P104" t="n">
-        <v>33559.17</v>
+        <v>259410.23</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
@@ -7193,12 +7195,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>FBA75686</t>
+          <t>FBA79995</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>B0B4G89VQJ</t>
+          <t>B0GW8VBCBL</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -7208,25 +7210,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>AM-W10</t>
+          <t>AM-C50</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>4934.296426588235</v>
+        <v>534.6565721999999</v>
       </c>
       <c r="I105" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -7241,13 +7243,13 @@
         <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>24327.52</v>
+        <v>12468.08</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -7258,12 +7260,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>FBA79005</t>
+          <t>FBA78204</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0C4YT43Z3</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7273,25 +7275,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>AM-W45</t>
+          <t>AM-C31</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Microphone Conference</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Wireless Conference Microphone</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
-        <v>2738.484882</v>
+        <v>3835.413</v>
       </c>
       <c r="I106" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -7303,17 +7305,15 @@
         <v>25</v>
       </c>
       <c r="M106" t="n">
-        <v>393</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>13</v>
-      </c>
-      <c r="P106" t="n">
-        <v>473448.05</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P106" t="inlineStr"/>
       <c r="Q106" t="inlineStr">
         <is>
           <t>2026-06-20</t>
@@ -7323,12 +7323,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>FBA79064</t>
+          <t>FBA75679</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>B0CJR76Y7G</t>
+          <t>B0B4JRQP22</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>AA-25</t>
+          <t>AA-02</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7353,10 +7353,10 @@
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>326.010105</v>
+        <v>1330.281037275</v>
       </c>
       <c r="I107" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -7368,16 +7368,16 @@
         <v>25</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="N107" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P107" t="n">
-        <v>34134.14</v>
+        <v>90068.31</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -7388,12 +7388,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>FBA75677</t>
+          <t>FBA75692</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B0B4G1HPL5</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7403,25 +7403,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>AM-C5</t>
+          <t>AM-C11</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Microphone Conference</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Conference Microphone</t>
+          <t>USB/XLR Dynamic Mic</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>1291.959696295941</v>
+        <v>2975.579697881559</v>
       </c>
       <c r="I108" t="n">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -7436,13 +7436,13 @@
         <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O108" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P108" t="n">
-        <v>113875.82</v>
+        <v>128349.42</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -7453,12 +7453,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>FBA76723</t>
+          <t>FBA79981</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>B0BLKF46QG</t>
+          <t>B0GN8MFDGZ</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7468,25 +7468,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>AM-C20</t>
+          <t>AK-61 Neo</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Electric Keyboard</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>61 Key Electronic Keyboard With LED DIsplay</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>1235.473403164659</v>
+        <v>2870.1202068</v>
       </c>
       <c r="I109" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -7498,16 +7498,16 @@
         <v>25</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N109" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P109" t="n">
-        <v>4669.47</v>
+        <v>90878.74000000001</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -7518,12 +7518,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>FBA76862</t>
+          <t>FBK79010</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
+          <t>B0FLYJFC22</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7533,25 +7533,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>AM-C28</t>
+          <t>AM-C42</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Microphone Conference</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Conference Microphone</t>
+          <t>USB Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>874.2436631991176</v>
+        <v>1499.646483</v>
       </c>
       <c r="I110" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -7563,16 +7563,16 @@
         <v>25</v>
       </c>
       <c r="M110" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="N110" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="P110" t="n">
-        <v>148733</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -7583,12 +7583,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>FBA79694</t>
+          <t>FBA79016</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>B0DT6T6N6B</t>
+          <t>B0CH4R1V6S</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7598,25 +7598,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>AA-26</t>
+          <t>AM-C3a</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>260.808084</v>
+        <v>521.6161679999999</v>
       </c>
       <c r="I111" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -7628,16 +7628,16 @@
         <v>25</v>
       </c>
       <c r="M111" t="n">
-        <v>526</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="O111" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="P111" t="n">
-        <v>41253.26</v>
+        <v>21130.15</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -7648,12 +7648,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>FBA79449</t>
+          <t>FBA76728</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>B0DFMNGFTD</t>
+          <t>B0BLNCP74M</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7663,25 +7663,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>AM-W36</t>
+          <t>AM-C25</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>USB Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>4042.525302</v>
+        <v>2157.615343358823</v>
       </c>
       <c r="I112" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -7696,14 +7696,12 @@
         <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>1</v>
-      </c>
-      <c r="P112" t="n">
-        <v>106514.53</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P112" t="inlineStr"/>
       <c r="Q112" t="inlineStr">
         <is>
           <t>2026-06-20</t>
@@ -7713,12 +7711,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FBA79830</t>
+          <t>FBA79909</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>B0FJ8TSQK1</t>
+          <t>B0FVM17Q4W</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7728,25 +7726,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>GB-03 (AI-12 + AM-C43)</t>
+          <t>AM-W20</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>GB-03</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>1828.2802</v>
+        <v>2164.7070972</v>
       </c>
       <c r="I113" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -7758,17 +7756,15 @@
         <v>25</v>
       </c>
       <c r="M113" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="N113" t="n">
         <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>5</v>
-      </c>
-      <c r="P113" t="n">
-        <v>29359.72</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P113" t="inlineStr"/>
       <c r="Q113" t="inlineStr">
         <is>
           <t>2026-06-20</t>
@@ -7778,12 +7774,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FBA79465</t>
+          <t>FBA80003</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>B0DFMQCGT1</t>
+          <t>B0GW92TTMS</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7793,25 +7789,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>AM-W21</t>
+          <t>AM-W32 Pro</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>Dual UHF Wireless Microphone With Receiver</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
-        <v>2803.686903</v>
+        <v>3129.697008</v>
       </c>
       <c r="I114" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -7823,7 +7819,7 @@
         <v>25</v>
       </c>
       <c r="M114" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
         <v>0</v>
@@ -7832,7 +7828,7 @@
         <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>4921.03</v>
+        <v>61869.39</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -7843,12 +7839,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>FBA75674</t>
+          <t>FBA79445</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0DFMLS8JG</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7858,25 +7854,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>AM-C2</t>
+          <t>AM-W32</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>XLR Microphone Kit - Boomarm</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>2119.874127397059</v>
+        <v>2167.31517804</v>
       </c>
       <c r="I115" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -7888,16 +7884,16 @@
         <v>25</v>
       </c>
       <c r="M115" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O115" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="P115" t="n">
-        <v>55783.47</v>
+        <v>62976.32</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -7908,12 +7904,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>FBA79654</t>
+          <t>FBA80009</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>B0DN6MNS1X</t>
+          <t>B0GW8R2RYM</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7923,7 +7919,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>AM-C11 Pro</t>
+          <t>AM-C51</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7933,15 +7929,15 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
-        <v>3140.890488</v>
+        <v>912.8282939999998</v>
       </c>
       <c r="I116" t="n">
-        <v>79</v>
+        <v>18</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -7956,13 +7952,13 @@
         <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P116" t="n">
-        <v>298226.44</v>
+        <v>22424.73</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -7973,12 +7969,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>FBA79840</t>
+          <t>FBA75689</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>B0FQBWV1ST</t>
+          <t>B0B4G59Y8W</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7988,25 +7984,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>AH-60-RD</t>
+          <t>AM-W13</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Headphone</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Headphone</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>1092.483648</v>
+        <v>1305.459898830882</v>
       </c>
       <c r="I117" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -8018,16 +8014,16 @@
         <v>25</v>
       </c>
       <c r="M117" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O117" t="n">
         <v>4</v>
       </c>
       <c r="P117" t="n">
-        <v>61960.89</v>
+        <v>18144.32</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -8038,12 +8034,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FBA79107</t>
+          <t>FBA75687</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B0B4G5ZLTB</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -8053,7 +8049,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>AM-W17</t>
+          <t>AM-W11</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -8063,15 +8059,15 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
-        <v>1043.232336</v>
+        <v>2857.758705882353</v>
       </c>
       <c r="I118" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -8086,13 +8082,13 @@
         <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P118" t="n">
-        <v>66470.32000000001</v>
+        <v>1885.92</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -8103,12 +8099,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>FBA79958</t>
+          <t>FBA79967</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0G2C2RCXN</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -8118,7 +8114,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>AM-W24</t>
+          <t>AM-W19</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -8133,10 +8129,10 @@
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>905.00405148</v>
+        <v>1159.29193338</v>
       </c>
       <c r="I119" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -8148,16 +8144,16 @@
         <v>25</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="N119" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P119" t="n">
-        <v>67344.32000000001</v>
+        <v>1481.65</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -8168,12 +8164,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>FBA79981</t>
+          <t>FBA75686</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>B0GN8MFDGZ</t>
+          <t>B0B4G89VQJ</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -8183,25 +8179,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>AK-61 Neo</t>
+          <t>AM-W10</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Electric Keyboard</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61 Key Electronic Keyboard With LED DIsplay</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>2870.1202068</v>
+        <v>4934.296426588235</v>
       </c>
       <c r="I120" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -8213,16 +8209,16 @@
         <v>25</v>
       </c>
       <c r="M120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O120" t="n">
         <v>1</v>
       </c>
       <c r="P120" t="n">
-        <v>90878.74000000001</v>
+        <v>24327.52</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -8233,12 +8229,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>FBA79106</t>
+          <t>FBA79823</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>B0CM9KJZWQ</t>
+          <t>B0FJ2HZCVN</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -8248,25 +8244,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>AM-C44</t>
+          <t>PB-01 (AM-C11 + AI-04)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dynamic Microphone</t>
+          <t>PB-01</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
-        <v>2738.484882</v>
+        <v>4859.948</v>
       </c>
       <c r="I121" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -8278,16 +8274,16 @@
         <v>25</v>
       </c>
       <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="n">
+        <v>12</v>
+      </c>
+      <c r="O121" t="n">
         <v>1</v>
       </c>
-      <c r="N121" t="n">
-        <v>11</v>
-      </c>
-      <c r="O121" t="n">
-        <v>2</v>
-      </c>
       <c r="P121" t="n">
-        <v>113110.12</v>
+        <v>82498.16</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -8298,12 +8294,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>FBA79848</t>
+          <t>FBA79449</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>B0GN97RFPR</t>
+          <t>B0DFMNGFTD</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -8313,25 +8309,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>AM-S2</t>
+          <t>AM-W36</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Monitor Speakers</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Studio Monitor Speaker</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>3748.5845172</v>
+        <v>4042.525302</v>
       </c>
       <c r="I122" t="n">
-        <v>319</v>
+        <v>24</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -8343,16 +8339,16 @@
         <v>25</v>
       </c>
       <c r="M122" t="n">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O122" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P122" t="n">
-        <v>1628020.69</v>
+        <v>106514.53</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -8363,12 +8359,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>FBA79103</t>
+          <t>FBA80010</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>B0CM6NTWBP</t>
+          <t>B0GW8ZQRFK</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -8378,25 +8374,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>AI-10</t>
+          <t>AM-C52</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>1499.646483</v>
+        <v>912.8282939999998</v>
       </c>
       <c r="I123" t="n">
-        <v>167</v>
+        <v>10</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -8408,16 +8404,16 @@
         <v>25</v>
       </c>
       <c r="M123" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N123" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P123" t="n">
-        <v>348909.37</v>
+        <v>12458.18</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -8428,12 +8424,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>FBA79836</t>
+          <t>FBA79904</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>B0FJ8Z1W81</t>
+          <t>B0FTVQQVDC</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8443,7 +8439,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>PB-07 (AA-05 + AM-C45 + AI-04)</t>
+          <t>PB-10 (AM-C2+AI-04+AH-60-BL)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -8453,15 +8449,15 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>PB-07</t>
+          <t>PB-10</t>
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
-        <v>4180.2798</v>
+        <v>4986.467599999999</v>
       </c>
       <c r="I124" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -8473,16 +8469,16 @@
         <v>25</v>
       </c>
       <c r="M124" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="N124" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
       </c>
       <c r="P124" t="n">
-        <v>49777.93</v>
+        <v>276512.04</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -8493,12 +8489,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>FBA79825</t>
+          <t>FBA79820</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>B0FJ2DT13L</t>
+          <t>B0FQJWWDVK</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8508,25 +8504,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>GB-02 (AM-C43 + AI-11)</t>
+          <t>AC-3XL</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>GB-02</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>1983.58</v>
+        <v>130.404042</v>
       </c>
       <c r="I125" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -8538,16 +8534,16 @@
         <v>25</v>
       </c>
       <c r="M125" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="N125" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>39076.66</v>
+        <v>10120.06</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -8558,12 +8554,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>FBA79980</t>
+          <t>FBA80002</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>B0GN8MMKY1</t>
+          <t>B0GW96SHSK</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8573,25 +8569,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>AK-37-W</t>
+          <t>AM-W33 Pro</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Electric Keyboard</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>37 Key Electronic Keyboard White</t>
+          <t>Single UHF Wireless Microphone With Receiver</t>
         </is>
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
-        <v>2335.8554064</v>
+        <v>1825.656588</v>
       </c>
       <c r="I126" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -8606,13 +8602,13 @@
         <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P126" t="n">
-        <v>30757.44</v>
+        <v>32713.83</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -8623,12 +8619,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>FBA79355</t>
+          <t>FBA79969</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>B0D3M86SH1</t>
+          <t>B0G3B677Z5</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8638,25 +8634,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>AA-19BL</t>
+          <t>UB-03 (AM-S1 + AA-22)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>UB-03</t>
         </is>
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>2973.2121576</v>
+        <v>5619.632</v>
       </c>
       <c r="I127" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -8668,16 +8664,16 @@
         <v>25</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N127" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P127" t="n">
-        <v>57654.05</v>
+        <v>145423.97</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -8688,12 +8684,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>FBA76722</t>
+          <t>FBA79009</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>B0BLKDC4PP</t>
+          <t>B0CH4PMR8K</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8703,7 +8699,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>AM-C19</t>
+          <t>AM-C41</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8718,10 +8714,10 @@
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
-        <v>1642.572937873306</v>
+        <v>1043.232336</v>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -8733,15 +8729,17 @@
         <v>25</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O128" t="n">
-        <v>0</v>
-      </c>
-      <c r="P128" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="P128" t="n">
+        <v>39920.09</v>
+      </c>
       <c r="Q128" t="inlineStr">
         <is>
           <t>2026-06-20</t>
@@ -8751,12 +8749,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>FBA76863</t>
+          <t>FBA79830</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>B0BPM2T7BQ</t>
+          <t>B0FJ8TSQK1</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8766,25 +8764,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>AI-03</t>
+          <t>GB-03 (AI-12 + AM-C43)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>GB-03</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
-        <v>2179.9269789525</v>
+        <v>1828.2802</v>
       </c>
       <c r="I129" t="n">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -8796,16 +8794,16 @@
         <v>25</v>
       </c>
       <c r="M129" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="N129" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P129" t="n">
-        <v>172634.98</v>
+        <v>29359.72</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -8816,12 +8814,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>FBA75691</t>
+          <t>FBA79465</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>B0B4G5JG4P</t>
+          <t>B0DFMQCGT1</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8831,25 +8829,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>AM-W14</t>
+          <t>AM-W21</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
-        <v>3221.74692</v>
+        <v>2803.686903</v>
       </c>
       <c r="I130" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -8861,16 +8859,16 @@
         <v>25</v>
       </c>
       <c r="M130" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="N130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P130" t="n">
-        <v>27824.26</v>
+        <v>4921.03</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -8881,12 +8879,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>FBA79996</t>
+          <t>FBA79832</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>B0GW8Z556N</t>
+          <t>B0FJ8S53GW</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8896,25 +8894,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>AM-C49</t>
+          <t>GB-05 (AM-C43 + AI-06)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>GB-05</t>
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>534.6565721999999</v>
+        <v>3909.104</v>
       </c>
       <c r="I131" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -8926,16 +8924,16 @@
         <v>25</v>
       </c>
       <c r="M131" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P131" t="n">
-        <v>9974.469999999999</v>
+        <v>88086.16</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -8946,12 +8944,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FBA79820</t>
+          <t>FBA79905</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>B0FQJWWDVK</t>
+          <t>B0FTVSH458</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8961,25 +8959,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>AC-3XL</t>
+          <t>PB-11 (AM-C44+AA-05+AH-45-BK)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>PB-11</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
-        <v>130.404042</v>
+        <v>3425.8468</v>
       </c>
       <c r="I132" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -8991,16 +8989,16 @@
         <v>25</v>
       </c>
       <c r="M132" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
       </c>
       <c r="P132" t="n">
-        <v>10120.06</v>
+        <v>10486.71</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -9011,12 +9009,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>FBA79108</t>
+          <t>FBA79841</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>B0CM9L1QZG</t>
+          <t>B0FQBTRM28</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -9026,25 +9024,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>AM-W16</t>
+          <t>AH-60-BL</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Headphone</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>Headphone</t>
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
-        <v>756.3434436</v>
+        <v>1092.483648</v>
       </c>
       <c r="I133" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -9056,16 +9054,16 @@
         <v>25</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N133" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="O133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P133" t="n">
-        <v>48344.26</v>
+        <v>79000.14</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -9076,12 +9074,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>FBA80016</t>
+          <t>FBA79821</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>B0GKPXQ8G3</t>
+          <t>B0FJ2JJZL3</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -9091,25 +9089,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>AM-W22</t>
+          <t>UB-01 (AI-04, AM-S1, AA-21, AM-C2)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>UB-01</t>
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>1679.6</v>
+        <v>9527.5088</v>
       </c>
       <c r="I134" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -9121,16 +9119,16 @@
         <v>25</v>
       </c>
       <c r="M134" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O134" t="n">
         <v>1</v>
       </c>
       <c r="P134" t="n">
-        <v>7444.46</v>
+        <v>58031.42</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -9141,12 +9139,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>FBA75681</t>
+          <t>FBA79824</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>B0B4FZS38V</t>
+          <t>B0FJ2K95XT</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -9156,25 +9154,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>AM-C7</t>
+          <t>GB-01 (AM-C43 +AI-10)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Boomarm</t>
+          <t>GB-01</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
-        <v>2051.276637829411</v>
+        <v>2585.9936</v>
       </c>
       <c r="I135" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -9189,13 +9187,13 @@
         <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
       </c>
       <c r="P135" t="n">
-        <v>2050.99</v>
+        <v>71307.37</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -9206,12 +9204,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>FBA79844</t>
+          <t>FBA79104</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>B0FN7DYB2M</t>
+          <t>B0CM6NVLT9</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -9221,25 +9219,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>PB-08 (AM-C1 + AI-04)</t>
+          <t>AI-11</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>PB-08</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
-        <v>3358.8228</v>
+        <v>847.6262729999999</v>
       </c>
       <c r="I136" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -9251,16 +9249,16 @@
         <v>25</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N136" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="O136" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="P136" t="n">
-        <v>5033.59</v>
+        <v>108615.8</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -9271,12 +9269,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>FBA75678</t>
+          <t>FBA80016</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>B0B4G8PH2P</t>
+          <t>B0GKPXQ8G3</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -9286,25 +9284,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>AA-01</t>
+          <t>AM-W22</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
-        <v>1224.499030661912</v>
+        <v>1679.6</v>
       </c>
       <c r="I137" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -9316,16 +9314,16 @@
         <v>25</v>
       </c>
       <c r="M137" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="N137" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P137" t="n">
-        <v>36692.4</v>
+        <v>7444.46</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -9336,12 +9334,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>FBA79972</t>
+          <t>FBA79813</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>B0GCP1J2HC</t>
+          <t>B0FG88HVQ8</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -9351,25 +9349,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>AH-50</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>DJ Headphone</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>8 channels Mixer</t>
+          <t>DJ Headphone</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
-        <v>4119.760313999999</v>
+        <v>1201.7320128</v>
       </c>
       <c r="I138" t="n">
-        <v>5</v>
+        <v>481</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -9381,16 +9379,16 @@
         <v>25</v>
       </c>
       <c r="M138" t="n">
-        <v>202</v>
+        <v>317</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O138" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="P138" t="n">
-        <v>29712.85</v>
+        <v>711190.58</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -9401,12 +9399,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>FBA79448</t>
+          <t>FBA75684</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>B0DFMKY4TT</t>
+          <t>B0B4G7VWXD</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -9416,25 +9414,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>AM-W35</t>
+          <t>AA-04</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
-        <v>1984.74951924</v>
+        <v>871.9473036705882</v>
       </c>
       <c r="I139" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -9446,16 +9444,16 @@
         <v>25</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N139" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O139" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="P139" t="n">
-        <v>29115.32</v>
+        <v>49936.45</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -9466,12 +9464,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>FBA75679</t>
+          <t>FBA78424</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>B0B4JRQP22</t>
+          <t>B0C55MY66L</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9481,25 +9479,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>AA-02</t>
+          <t>AM-C37</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>USB/XLR Dynamic Mic</t>
         </is>
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
-        <v>1330.281037275</v>
+        <v>3103.426797881559</v>
       </c>
       <c r="I140" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -9511,16 +9509,16 @@
         <v>25</v>
       </c>
       <c r="M140" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
         <v>1</v>
       </c>
-      <c r="O140" t="n">
-        <v>2</v>
-      </c>
       <c r="P140" t="n">
-        <v>90068.31</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -9531,12 +9529,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>FBA78204</t>
+          <t>FBA75691</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>B0C4YT43Z3</t>
+          <t>B0B4G5JG4P</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9546,25 +9544,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>AM-C31</t>
+          <t>AM-W14</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
-        <v>3835.413</v>
+        <v>3221.74692</v>
       </c>
       <c r="I141" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -9576,15 +9574,17 @@
         <v>25</v>
       </c>
       <c r="M141" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O141" t="n">
-        <v>0</v>
-      </c>
-      <c r="P141" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="P141" t="n">
+        <v>27824.26</v>
+      </c>
       <c r="Q141" t="inlineStr">
         <is>
           <t>2026-06-20</t>
